--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0002T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.01817379631922</v>
+        <v>5.690453241901874</v>
       </c>
       <c r="D2" t="n">
-        <v>34.67430337696261</v>
+        <v>5.634574298756425</v>
       </c>
       <c r="E2" t="n">
-        <v>10.96510291791971</v>
+        <v>1.781829224161953</v>
       </c>
       <c r="F2" t="n">
-        <v>10.91192952956838</v>
+        <v>1.773188548554861</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.72212533213516</v>
+        <v>7.592345366471965</v>
       </c>
       <c r="D3" t="n">
-        <v>46.55626126339817</v>
+        <v>7.565392455302203</v>
       </c>
       <c r="E3" t="n">
-        <v>10.96510291791971</v>
+        <v>1.781829224161953</v>
       </c>
       <c r="F3" t="n">
-        <v>10.91192952956838</v>
+        <v>1.773188548554861</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.20809202095634</v>
+        <v>3.933814953405405</v>
       </c>
       <c r="D4" t="n">
-        <v>24.30643077318368</v>
+        <v>3.949795000642348</v>
       </c>
       <c r="E4" t="n">
-        <v>10.96510291791971</v>
+        <v>1.781829224161953</v>
       </c>
       <c r="F4" t="n">
-        <v>10.91192952956838</v>
+        <v>1.773188548554861</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.42288615570496</v>
+        <v>2.018719000302056</v>
       </c>
       <c r="D5" t="n">
-        <v>12.5186970196018</v>
+        <v>2.034288265685293</v>
       </c>
       <c r="E5" t="n">
-        <v>10.96510291791971</v>
+        <v>1.781829224161953</v>
       </c>
       <c r="F5" t="n">
-        <v>10.91192952956838</v>
+        <v>1.773188548554861</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.68856345723527</v>
+        <v>5.311891561800731</v>
       </c>
       <c r="D6" t="n">
-        <v>32.84548421314807</v>
+        <v>5.337391184636561</v>
       </c>
       <c r="E6" t="n">
-        <v>10.96510291791971</v>
+        <v>1.781829224161953</v>
       </c>
       <c r="F6" t="n">
-        <v>10.91192952956838</v>
+        <v>1.773188548554861</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.12693740285402</v>
+        <v>7.333127327963778</v>
       </c>
       <c r="D7" t="n">
-        <v>45.21834169658095</v>
+        <v>7.347980525694404</v>
       </c>
       <c r="E7" t="n">
-        <v>10.96510291791971</v>
+        <v>1.781829224161953</v>
       </c>
       <c r="F7" t="n">
-        <v>10.91192952956838</v>
+        <v>1.773188548554861</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.2013513152263</v>
+        <v>5.557719588724273</v>
       </c>
       <c r="D8" t="n">
-        <v>34.59801829922049</v>
+        <v>5.62217797362333</v>
       </c>
       <c r="E8" t="n">
-        <v>10.96510291791971</v>
+        <v>1.781829224161953</v>
       </c>
       <c r="F8" t="n">
-        <v>10.91192952956838</v>
+        <v>1.773188548554861</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
